--- a/public/exports-from-60-with-coowners/55606617.xlsx
+++ b/public/exports-from-60-with-coowners/55606617.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311674028</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">

--- a/public/exports-from-60-with-coowners/55606617.xlsx
+++ b/public/exports-from-60-with-coowners/55606617.xlsx
@@ -11839,7 +11839,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674028</t>
+          <t xml:space="preserve">311674027</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">

--- a/public/exports-from-60-with-coowners/55606617.xlsx
+++ b/public/exports-from-60-with-coowners/55606617.xlsx
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 8</t>
+          <t xml:space="preserve">Sollentuna Alle 4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J37">
-        <v>537</v>
+        <v>445</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585999</t>
+          <t xml:space="preserve">311586007</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 4</t>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2831,11 +2831,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38">
-        <v>445</v>
+        <v>1324</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2906,11 +2906,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J39">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2981,11 +2981,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J40">
-        <v>1320</v>
+        <v>493</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3056,11 +3056,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J41">
-        <v>493</v>
+        <v>172</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3131,11 +3131,11 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J42">
-        <v>172</v>
+        <v>1324</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3206,11 +3206,11 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J43">
-        <v>1324</v>
+        <v>1018</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 6</t>
+          <t xml:space="preserve">Høvedstensvej 35</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,20 +3276,20 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2091192</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J44">
-        <v>1018</v>
+        <v>8026</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586007</t>
+          <t xml:space="preserve">311566793</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-08</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 35</t>
+          <t xml:space="preserve">Catherine Boothsvej 22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,30 +3351,30 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091192</t>
+          <t xml:space="preserve">2079383</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J45">
-        <v>8026</v>
+        <v>595</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566793</t>
+          <t xml:space="preserve">311567481</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-08</t>
+          <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catherine Boothsvej 22</t>
+          <t xml:space="preserve">Catherine Boothsvej 24A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3431,11 +3431,11 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J46">
-        <v>595</v>
+        <v>743</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catherine Boothsvej 24A</t>
+          <t xml:space="preserve">Catherine Boothsvej 24D</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3506,11 +3506,11 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J47">
-        <v>743</v>
+        <v>202</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catherine Boothsvej 24D</t>
+          <t xml:space="preserve">Bødkerporten 1Y</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,30 +3576,30 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079383</t>
+          <t xml:space="preserve">2159266</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>202</v>
+        <v>7598</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567481</t>
+          <t xml:space="preserve">311586010</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-13</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkerporten 1Y</t>
+          <t xml:space="preserve">Hvidovrevej 218</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,20 +3651,20 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159266</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J49">
-        <v>7598</v>
+        <v>1337</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586010</t>
+          <t xml:space="preserve">311588713</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 218</t>
+          <t xml:space="preserve">Hvidovrevej 440</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,20 +3726,20 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J50">
-        <v>1337</v>
+        <v>863</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588713</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3806,11 +3806,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J51">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3881,11 +3881,11 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J52">
-        <v>861</v>
+        <v>958</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3956,11 +3956,11 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J53">
-        <v>958</v>
+        <v>858</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 440</t>
+          <t xml:space="preserve">Hvidovrevej 440A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4031,11 +4031,11 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J54">
-        <v>858</v>
+        <v>6125</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 440A</t>
+          <t xml:space="preserve">Egevolden 106</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,20 +4101,20 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J55">
-        <v>6125</v>
+        <v>4371</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586013</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-01-11</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4181,11 +4181,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J56">
-        <v>4371</v>
+        <v>2187</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4256,11 +4256,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J57">
-        <v>2187</v>
+        <v>362</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevolden 106</t>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,20 +4326,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J58">
-        <v>362</v>
+        <v>894</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586013</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-11</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4406,11 +4406,11 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J59">
-        <v>894</v>
+        <v>568</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4481,11 +4481,11 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J60">
-        <v>568</v>
+        <v>493</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4556,11 +4556,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J61">
-        <v>493</v>
+        <v>449</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4631,11 +4631,11 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J62">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4706,11 +4706,11 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J63">
-        <v>445</v>
+        <v>798</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J64">
@@ -4856,11 +4856,11 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J65">
-        <v>798</v>
+        <v>772</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4931,11 +4931,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J66">
-        <v>772</v>
+        <v>884</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5006,11 +5006,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J67">
-        <v>884</v>
+        <v>621</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J68">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J69">
@@ -5231,11 +5231,11 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J70">
-        <v>621</v>
+        <v>1214</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+          <t xml:space="preserve">Kettegård Alle 2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>1214</v>
+        <v>1703</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588729</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 2</t>
+          <t xml:space="preserve">Kettegård Alle 2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,20 +5376,20 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J72">
-        <v>969</v>
+        <v>663</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588722</t>
+          <t xml:space="preserve">311588729</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 4</t>
+          <t xml:space="preserve">Kettegård Alle 2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,20 +5451,20 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J73">
-        <v>5857</v>
+        <v>273</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588721</t>
+          <t xml:space="preserve">311588729</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J74">
-        <v>1703</v>
+        <v>1925</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 2</t>
+          <t xml:space="preserve">Kettegård Alle 4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5606,11 +5606,11 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J75">
-        <v>663</v>
+        <v>1256</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 2</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,20 +5676,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>273</v>
+        <v>3240</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311588726</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 2</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,20 +5751,20 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J77">
-        <v>1925</v>
+        <v>554</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311588726</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 4</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J78">
-        <v>1256</v>
+        <v>1528</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311588726</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5906,11 +5906,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J79">
-        <v>3240</v>
+        <v>2017</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5981,11 +5981,11 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J80">
-        <v>554</v>
+        <v>1008</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6056,11 +6056,11 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J81">
-        <v>1528</v>
+        <v>218</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6131,11 +6131,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J82">
-        <v>2017</v>
+        <v>900</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,20 +6201,20 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J83">
-        <v>1008</v>
+        <v>326</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,20 +6276,20 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J84">
-        <v>218</v>
+        <v>1167</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,20 +6351,20 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J85">
-        <v>900</v>
+        <v>629</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6431,11 +6431,11 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J86">
-        <v>326</v>
+        <v>785</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6506,11 +6506,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J87">
-        <v>1167</v>
+        <v>629</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J88">
-        <v>629</v>
+        <v>1151</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6656,11 +6656,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J89">
-        <v>785</v>
+        <v>571</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Byvej 78</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,30 +6726,30 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2157348</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>629</v>
+        <v>262</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311590033</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,30 +6801,30 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J91">
-        <v>1151</v>
+        <v>2799</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311590065</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,30 +6876,30 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J92">
-        <v>571</v>
+        <v>1487</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311590063</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 78</t>
+          <t xml:space="preserve">Sollentuna Alle 4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,20 +6951,20 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157348</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J93">
-        <v>262</v>
+        <v>2387</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590033</t>
+          <t xml:space="preserve">311590061</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J94">
-        <v>2799</v>
+        <v>787</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590065</t>
+          <t xml:space="preserve">311590058</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Trædrejerporten 1A</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,20 +7101,20 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2159280</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J95">
-        <v>1487</v>
+        <v>5757</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590063</t>
+          <t xml:space="preserve">311589965</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 4</t>
+          <t xml:space="preserve">M Bechs Alle 122</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,30 +7176,30 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J96">
-        <v>2387</v>
+        <v>1272</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590061</t>
+          <t xml:space="preserve">311590424</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 6</t>
+          <t xml:space="preserve">M Bechs Alle 122</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7251,30 +7251,30 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J97">
-        <v>787</v>
+        <v>4563</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590058</t>
+          <t xml:space="preserve">311590424</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trædrejerporten 1A</t>
+          <t xml:space="preserve">M Bechs Alle 122B</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7326,30 +7326,30 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159280</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J98">
-        <v>5757</v>
+        <v>2141</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589965</t>
+          <t xml:space="preserve">311590424</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,30 +7401,30 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J99">
-        <v>1272</v>
+        <v>904</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590424</t>
+          <t xml:space="preserve">311598300</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Kommune</t>
+          <t xml:space="preserve">Lejerbo, Hvidovre</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122</t>
+          <t xml:space="preserve">Søvangsvej 20</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,30 +7476,30 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">220589, 220590</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>4563</v>
+        <v>710</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590424</t>
+          <t xml:space="preserve">311599910</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-05-12</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122B</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,30 +7551,30 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J101">
-        <v>2141</v>
+        <v>839</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590424</t>
+          <t xml:space="preserve">311601624</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7631,15 +7631,15 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J102">
-        <v>904</v>
+        <v>863</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598300</t>
+          <t xml:space="preserve">311601624</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejerbo, Hvidovre</t>
+          <t xml:space="preserve">Hvidovre Kommune</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvangsvej 20</t>
+          <t xml:space="preserve">Egevolden 100</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,30 +7701,30 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">220589, 220590</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J103">
-        <v>710</v>
+        <v>468</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599910</t>
+          <t xml:space="preserve">311601932</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-12</t>
+          <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Kommune</t>
+          <t xml:space="preserve">Lejerbo, Hvidovre</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Holmelundsvej 1</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,30 +7776,30 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">221098, 221099</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J104">
-        <v>839</v>
+        <v>1194</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601624</t>
+          <t xml:space="preserve">311602604</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-19</t>
+          <t xml:space="preserve">2032-05-24</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Kommune</t>
+          <t xml:space="preserve">Lejerbo, Hvidovre</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Holmelundsvej 5</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,30 +7851,30 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">221098, 221100</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J105">
-        <v>863</v>
+        <v>733</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601624</t>
+          <t xml:space="preserve">311602604</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-19</t>
+          <t xml:space="preserve">2032-05-24</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevolden 100</t>
+          <t xml:space="preserve">Avedøre Tværvej 135B</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,20 +7926,20 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">2159316</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>468</v>
+        <v>356</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601932</t>
+          <t xml:space="preserve">311622352</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-20</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejerbo, Hvidovre</t>
+          <t xml:space="preserve">Hvidovre Kommune</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmelundsvej 1</t>
+          <t xml:space="preserve">Avedøre Tværvej 135B</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,30 +8001,30 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">221098, 221099</t>
+          <t xml:space="preserve">2159316</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J107">
-        <v>1194</v>
+        <v>199</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311602604</t>
+          <t xml:space="preserve">311622354</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-24</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejerbo, Hvidovre</t>
+          <t xml:space="preserve">Hvidovre Kommune</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmelundsvej 5</t>
+          <t xml:space="preserve">Bibliotekvej 62</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,30 +8076,30 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">221098, 221100</t>
+          <t xml:space="preserve">2091211</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J108">
-        <v>733</v>
+        <v>1472</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311602604</t>
+          <t xml:space="preserve">311622365</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-24</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avedøre Tværvej 135B</t>
+          <t xml:space="preserve">Byvej 78</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,20 +8151,20 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159316</t>
+          <t xml:space="preserve">7029060</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J109">
-        <v>356</v>
+        <v>398</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622352</t>
+          <t xml:space="preserve">311622350</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avedøre Tværvej 135B</t>
+          <t xml:space="preserve">Bødkerporten 6B</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,20 +8226,20 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159316</t>
+          <t xml:space="preserve">2159279</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J110">
-        <v>199</v>
+        <v>1712</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622354</t>
+          <t xml:space="preserve">311622355</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekvej 62</t>
+          <t xml:space="preserve">Egevolden 106</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,20 +8301,20 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091211</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J111">
-        <v>1472</v>
+        <v>3349</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622365</t>
+          <t xml:space="preserve">311622381</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 78</t>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,20 +8376,20 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">7029060</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J112">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622350</t>
+          <t xml:space="preserve">311622362</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkerporten 6B</t>
+          <t xml:space="preserve">Hvidovrevej 272</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159279</t>
+          <t xml:space="preserve">2091208</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>1712</v>
+        <v>2623</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622355</t>
+          <t xml:space="preserve">311622363</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevolden 106</t>
+          <t xml:space="preserve">Hvidovrevej 446</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,20 +8526,20 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J114">
-        <v>3349</v>
+        <v>4389</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622381</t>
+          <t xml:space="preserve">311622359</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+          <t xml:space="preserve">Hvidovrevej 241</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,20 +8601,20 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">2090160</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J115">
-        <v>402</v>
+        <v>2533</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622362</t>
+          <t xml:space="preserve">311623162</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 272</t>
+          <t xml:space="preserve">Plovheldvej 4A</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,30 +8676,30 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091208</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J116">
-        <v>2623</v>
+        <v>1662</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622363</t>
+          <t xml:space="preserve">311641604</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-11-09</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 446</t>
+          <t xml:space="preserve">Plovheldvej 4A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,30 +8751,30 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J117">
-        <v>4389</v>
+        <v>323</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622359</t>
+          <t xml:space="preserve">311641603</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-11-09</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 241</t>
+          <t xml:space="preserve">Plovheldvej 4A</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,30 +8826,30 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090160</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J118">
-        <v>2533</v>
+        <v>2375</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623162</t>
+          <t xml:space="preserve">311644178</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8906,15 +8906,15 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J119">
-        <v>1662</v>
+        <v>1847</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641604</t>
+          <t xml:space="preserve">311644178</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-09</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8981,15 +8981,15 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J120">
-        <v>323</v>
+        <v>1226</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641603</t>
+          <t xml:space="preserve">311644178</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-09</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9056,11 +9056,11 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J121">
-        <v>2375</v>
+        <v>1301</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -9131,11 +9131,11 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J122">
-        <v>1847</v>
+        <v>2569</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -9206,11 +9206,11 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J123">
-        <v>1226</v>
+        <v>606</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plovheldvej 4A</t>
+          <t xml:space="preserve">Høvedstensvej 37</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,30 +9276,30 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">2091192</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J124">
-        <v>1301</v>
+        <v>110</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311653142</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-01-10</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plovheldvej 4A</t>
+          <t xml:space="preserve">Hvidovrevej 278</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,30 +9351,30 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>2569</v>
+        <v>1345</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311669671</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plovheldvej 4A</t>
+          <t xml:space="preserve">Hvidovrevej 278</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,30 +9426,30 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J126">
-        <v>606</v>
+        <v>6142</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311669668</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 37</t>
+          <t xml:space="preserve">Hvidovrevej 278</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,20 +9501,20 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091192</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J127">
-        <v>110</v>
+        <v>3329</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653142</t>
+          <t xml:space="preserve">311669668</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-10</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 6</t>
+          <t xml:space="preserve">Hvidovrevej 446</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,20 +9576,20 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J128">
-        <v>133</v>
+        <v>6161</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669682</t>
+          <t xml:space="preserve">311669688</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 278</t>
+          <t xml:space="preserve">Høvedstensvej 19</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,11 +9660,11 @@
         </is>
       </c>
       <c r="J129">
-        <v>1345</v>
+        <v>1000</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669671</t>
+          <t xml:space="preserve">311669683</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 278</t>
+          <t xml:space="preserve">Høvedstensvej 19</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,20 +9726,20 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J130">
-        <v>6142</v>
+        <v>580</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669668</t>
+          <t xml:space="preserve">311669684</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 278</t>
+          <t xml:space="preserve">Høvedstensvej 19</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,20 +9801,20 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J131">
-        <v>3329</v>
+        <v>178</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669668</t>
+          <t xml:space="preserve">311669685</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 446</t>
+          <t xml:space="preserve">Høvedstensvej 21</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J132">
-        <v>6161</v>
+        <v>1611</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669688</t>
+          <t xml:space="preserve">311669683</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 19</t>
+          <t xml:space="preserve">Høvedstensvej 21</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9956,15 +9956,15 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J133">
-        <v>1000</v>
+        <v>1223</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669683</t>
+          <t xml:space="preserve">311669685</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 19</t>
+          <t xml:space="preserve">Idrætsvej 88</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,11 +10035,11 @@
         </is>
       </c>
       <c r="J134">
-        <v>580</v>
+        <v>103</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669684</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 19</t>
+          <t xml:space="preserve">Karise Alle 29</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,20 +10101,20 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">226182</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J135">
-        <v>178</v>
+        <v>1836</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669685</t>
+          <t xml:space="preserve">311669673</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 21</t>
+          <t xml:space="preserve">Karise Alle 31</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">226183</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,11 +10185,11 @@
         </is>
       </c>
       <c r="J136">
-        <v>1611</v>
+        <v>3484</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669683</t>
+          <t xml:space="preserve">311669673</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 21</t>
+          <t xml:space="preserve">Krogstens Alle 51</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">226183</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J137">
-        <v>1223</v>
+        <v>3648</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669685</t>
+          <t xml:space="preserve">311669673</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 88</t>
+          <t xml:space="preserve">Plovheldvej 2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,20 +10326,20 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J138">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669680</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karise Alle 29</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,20 +10401,20 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">226182</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J139">
-        <v>1836</v>
+        <v>96</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669673</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karise Alle 31</t>
+          <t xml:space="preserve">Avedøre Havnevej 37</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,20 +10476,20 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">226183</t>
+          <t xml:space="preserve">7706803</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>3484</v>
+        <v>1559</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669673</t>
+          <t xml:space="preserve">311670403</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogstens Alle 51</t>
+          <t xml:space="preserve">Bibliotekvej 52A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,30 +10551,30 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">226183</t>
+          <t xml:space="preserve">100191021</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J141">
-        <v>3648</v>
+        <v>569</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669673</t>
+          <t xml:space="preserve">311670402</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plovheldvej 2</t>
+          <t xml:space="preserve">Byvej 98</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,20 +10626,20 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">7029060</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J142">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669678</t>
+          <t xml:space="preserve">311670169</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Hovedporten 1</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,20 +10701,20 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">8490056</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J143">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669679</t>
+          <t xml:space="preserve">311670178</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avedøre Havnevej 37</t>
+          <t xml:space="preserve">Hovedporten 2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">7706803</t>
+          <t xml:space="preserve">8490057</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>1559</v>
+        <v>141</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670403</t>
+          <t xml:space="preserve">311670173</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekvej 52A</t>
+          <t xml:space="preserve">M Bechs Alle 122</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,25 +10851,25 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">100191021</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>569</v>
+        <v>108</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670402</t>
+          <t xml:space="preserve">311670133</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 98</t>
+          <t xml:space="preserve">M Bechs Alle 122C</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">7029060</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J146">
-        <v>159</v>
+        <v>263</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670169</t>
+          <t xml:space="preserve">311670166</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 2</t>
+          <t xml:space="preserve">Tavlekærsvej 164</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,20 +11001,20 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">228813</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J147">
-        <v>92</v>
+        <v>4660</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670404</t>
+          <t xml:space="preserve">311670401</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedporten 1</t>
+          <t xml:space="preserve">Tavlekærsvej 166</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,20 +11076,20 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490056</t>
+          <t xml:space="preserve">228812</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J148">
-        <v>99</v>
+        <v>1671</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670178</t>
+          <t xml:space="preserve">311670400</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedporten 2</t>
+          <t xml:space="preserve">Østre Messegade 3</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,20 +11151,20 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490057</t>
+          <t xml:space="preserve">9889328</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J149">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670173</t>
+          <t xml:space="preserve">311670118</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122</t>
+          <t xml:space="preserve">Høvedstensvej 45</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>108</v>
+        <v>1130</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670133</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122C</t>
+          <t xml:space="preserve">Høvedstensvej 45</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,20 +11301,20 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J151">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670166</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tavlekærsvej 164</t>
+          <t xml:space="preserve">Høvedstensvej 45B</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,20 +11376,20 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">228813</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J152">
-        <v>4660</v>
+        <v>1050</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670401</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tavlekærsvej 166</t>
+          <t xml:space="preserve">Høvedstensvej 47</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,20 +11451,20 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">228812</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J153">
-        <v>1671</v>
+        <v>246</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670400</t>
+          <t xml:space="preserve">311674027</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Messegade 3</t>
+          <t xml:space="preserve">Høvedstensvej 49</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,20 +11526,20 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889328</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J154">
-        <v>126</v>
+        <v>865</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670118</t>
+          <t xml:space="preserve">311674026</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 45</t>
+          <t xml:space="preserve">Alarmpladsen 3</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,20 +11601,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">9494877</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J155">
-        <v>1130</v>
+        <v>365</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311707954</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-09-15</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 45</t>
+          <t xml:space="preserve">Alarmpladsen 6A</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,20 +11676,20 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">8490054</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J156">
-        <v>283</v>
+        <v>366</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311716208</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 45B</t>
+          <t xml:space="preserve">Byvej 248A</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,20 +11751,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J157">
-        <v>1050</v>
+        <v>619</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311716210</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 47</t>
+          <t xml:space="preserve">Byvej 248B</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,20 +11826,20 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J158">
-        <v>246</v>
+        <v>608</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311716211</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 49</t>
+          <t xml:space="preserve">Byvej 248C</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,20 +11901,20 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J159">
-        <v>865</v>
+        <v>619</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674026</t>
+          <t xml:space="preserve">311716212</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarmpladsen 3</t>
+          <t xml:space="preserve">Byvej 90</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,20 +11976,20 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9494877</t>
+          <t xml:space="preserve">2157348</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J160">
-        <v>365</v>
+        <v>680</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311707954</t>
+          <t xml:space="preserve">311716215</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-15</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarmpladsen 6A</t>
+          <t xml:space="preserve">Byvej 90B</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,20 +12051,20 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490054</t>
+          <t xml:space="preserve">2157348</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J161">
-        <v>366</v>
+        <v>284</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716208</t>
+          <t xml:space="preserve">311716216</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 248A</t>
+          <t xml:space="preserve">Bødkerporten 2D</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,20 +12126,20 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">2159279</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J162">
-        <v>619</v>
+        <v>351</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716210</t>
+          <t xml:space="preserve">311716218</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 248B</t>
+          <t xml:space="preserve">Bødkerporten 4</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,20 +12201,20 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">2159279</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J163">
-        <v>608</v>
+        <v>1201</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716211</t>
+          <t xml:space="preserve">311716217</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 248C</t>
+          <t xml:space="preserve">Fægtesalsvej 11</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,20 +12276,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">9889335</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="J164">
-        <v>619</v>
+        <v>687</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716212</t>
+          <t xml:space="preserve">311716220</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 90</t>
+          <t xml:space="preserve">Fægtesalsvej 5</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157348</t>
+          <t xml:space="preserve">9889336</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J165">
-        <v>680</v>
+        <v>1253</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716215</t>
+          <t xml:space="preserve">311716222</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 90B</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157348</t>
+          <t xml:space="preserve">2077515</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J166">
-        <v>284</v>
+        <v>685</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716216</t>
+          <t xml:space="preserve">311716223</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkerporten 2D</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,20 +12501,20 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159279</t>
+          <t xml:space="preserve">2077515</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J167">
-        <v>351</v>
+        <v>685</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716218</t>
+          <t xml:space="preserve">311716224</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkerporten 4</t>
+          <t xml:space="preserve">Hvidovrevej 65</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159279</t>
+          <t xml:space="preserve">2023609</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>1201</v>
+        <v>1289</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716217</t>
+          <t xml:space="preserve">311716225</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fægtesalsvej 11</t>
+          <t xml:space="preserve">Svendebjergvej 2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889335</t>
+          <t xml:space="preserve">2079445</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J169">
-        <v>687</v>
+        <v>616</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716220</t>
+          <t xml:space="preserve">311716226</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fægtesalsvej 5</t>
+          <t xml:space="preserve">Vedbyholm 8</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,20 +12726,20 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889336</t>
+          <t xml:space="preserve">2160430</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J170">
-        <v>1253</v>
+        <v>589</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716222</t>
+          <t xml:space="preserve">311716227</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
+          <t xml:space="preserve">Vestre Kvartergade 20</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,20 +12801,20 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077515</t>
+          <t xml:space="preserve">9889332</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="J171">
-        <v>685</v>
+        <v>423</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716223</t>
+          <t xml:space="preserve">311716230</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
+          <t xml:space="preserve">Vestre Kvartergade 22</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,20 +12876,20 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077515</t>
+          <t xml:space="preserve">9889334</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="J172">
-        <v>685</v>
+        <v>423</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716224</t>
+          <t xml:space="preserve">311716229</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 65</t>
+          <t xml:space="preserve">Vestre Kvartergade 5</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,20 +12951,20 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023609</t>
+          <t xml:space="preserve">9889329</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J173">
-        <v>1289</v>
+        <v>335</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716225</t>
+          <t xml:space="preserve">311716228</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendebjergvej 2</t>
+          <t xml:space="preserve">Hovedporten 6</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,20 +13026,20 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079445</t>
+          <t xml:space="preserve">8490055</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J174">
-        <v>616</v>
+        <v>736</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716226</t>
+          <t xml:space="preserve">311723773</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vedbyholm 8</t>
+          <t xml:space="preserve">Idrætsvej 75</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160430</t>
+          <t xml:space="preserve">2079621</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -13110,11 +13110,11 @@
         </is>
       </c>
       <c r="J175">
-        <v>589</v>
+        <v>916</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716227</t>
+          <t xml:space="preserve">311726046</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Kvartergade 20</t>
+          <t xml:space="preserve">Bibliotekvej 52A</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,30 +13176,30 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889332</t>
+          <t xml:space="preserve">100191021</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J176">
-        <v>423</v>
+        <v>98</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716230</t>
+          <t xml:space="preserve">311740622</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2034-02-22</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Kvartergade 22</t>
+          <t xml:space="preserve">Byvej 56</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889334</t>
+          <t xml:space="preserve">2157286</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>423</v>
+        <v>563</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716229</t>
+          <t xml:space="preserve">311740693</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2034-02-23</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Kvartergade 5</t>
+          <t xml:space="preserve">Bibliotekvej 60C</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,20 +13326,20 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889329</t>
+          <t xml:space="preserve">2091215</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J178">
-        <v>335</v>
+        <v>239</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716228</t>
+          <t xml:space="preserve">311814926</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedporten 6</t>
+          <t xml:space="preserve">Bytoften 29</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490055</t>
+          <t xml:space="preserve">2025808</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J179">
-        <v>736</v>
+        <v>781</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723773</t>
+          <t xml:space="preserve">311814922</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 75</t>
+          <t xml:space="preserve">Bytoften 29</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,20 +13476,20 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079621</t>
+          <t xml:space="preserve">2025808</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J180">
-        <v>916</v>
+        <v>856</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726046</t>
+          <t xml:space="preserve">311814922</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-30</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekvej 52A</t>
+          <t xml:space="preserve">Bytoften 29</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,30 +13551,30 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">100191021</t>
+          <t xml:space="preserve">2025808</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J181">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740622</t>
+          <t xml:space="preserve">311814922</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-22</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 56</t>
+          <t xml:space="preserve">Byvej 118</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157286</t>
+          <t xml:space="preserve">2157369</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13635,11 +13635,11 @@
         </is>
       </c>
       <c r="J182">
-        <v>563</v>
+        <v>230</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740693</t>
+          <t xml:space="preserve">311814933</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-23</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekvej 60C</t>
+          <t xml:space="preserve">Ejby Alle 34</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091215</t>
+          <t xml:space="preserve">9807242</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13710,11 +13710,11 @@
         </is>
       </c>
       <c r="J183">
-        <v>239</v>
+        <v>1483</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814926</t>
+          <t xml:space="preserve">311814923</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13761,22 +13761,22 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 29</t>
+          <t xml:space="preserve">Ericavej 2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">4560</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025808</t>
+          <t xml:space="preserve">2449037</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>781</v>
+        <v>131</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814922</t>
+          <t xml:space="preserve">311814927</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13836,22 +13836,22 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 29</t>
+          <t xml:space="preserve">Ericavej 2</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">4560</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025808</t>
+          <t xml:space="preserve">2449037</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>856</v>
+        <v>131</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814922</t>
+          <t xml:space="preserve">311814927</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13911,22 +13911,22 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 29</t>
+          <t xml:space="preserve">Ericavej 2</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">4560</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025808</t>
+          <t xml:space="preserve">2449037</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,11 +13935,11 @@
         </is>
       </c>
       <c r="J186">
-        <v>64</v>
+        <v>247</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814922</t>
+          <t xml:space="preserve">311814927</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13986,35 +13986,35 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 118</t>
+          <t xml:space="preserve">Ericavej 2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">4560</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157369</t>
+          <t xml:space="preserve">2449037</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J187">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814933</t>
+          <t xml:space="preserve">311814927</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14061,35 +14061,35 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejby Alle 34</t>
+          <t xml:space="preserve">Ericavej 2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">4560</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">9807242</t>
+          <t xml:space="preserve">2449037</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J188">
-        <v>1483</v>
+        <v>137</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814923</t>
+          <t xml:space="preserve">311814927</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14136,22 +14136,22 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ericavej 2</t>
+          <t xml:space="preserve">Gammel Køge Landevej 276</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4560</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2449037</t>
+          <t xml:space="preserve">7028595</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>131</v>
+        <v>416</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814927</t>
+          <t xml:space="preserve">311814918</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14211,35 +14211,35 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ericavej 2</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">4560</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2449037</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J190">
-        <v>131</v>
+        <v>430</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814927</t>
+          <t xml:space="preserve">311814920</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14286,35 +14286,35 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ericavej 2</t>
+          <t xml:space="preserve">Hvidovregade 20</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4560</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2449037</t>
+          <t xml:space="preserve">2025809</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>247</v>
+        <v>96</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814927</t>
+          <t xml:space="preserve">311814925</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14361,35 +14361,35 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ericavej 2</t>
+          <t xml:space="preserve">Hvidovregade 20</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4560</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2449037</t>
+          <t xml:space="preserve">2025809</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J192">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814927</t>
+          <t xml:space="preserve">311814925</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14436,35 +14436,35 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ericavej 2</t>
+          <t xml:space="preserve">Hvidovregade 20</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4560</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2449037</t>
+          <t xml:space="preserve">2025809</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J193">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814927</t>
+          <t xml:space="preserve">311814925</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Køge Landevej 276</t>
+          <t xml:space="preserve">Hvidovregade 49</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028595</t>
+          <t xml:space="preserve">8101016</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,11 +14535,11 @@
         </is>
       </c>
       <c r="J194">
-        <v>416</v>
+        <v>938</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814918</t>
+          <t xml:space="preserve">311814900</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Hvidovregade 59</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14601,20 +14601,20 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2025855</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J195">
-        <v>430</v>
+        <v>361</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814920</t>
+          <t xml:space="preserve">311814917</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 20</t>
+          <t xml:space="preserve">Næsborgvej 90</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025809</t>
+          <t xml:space="preserve">7028766</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814925</t>
+          <t xml:space="preserve">311814924</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 20</t>
+          <t xml:space="preserve">Næsborgvej 90</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025809</t>
+          <t xml:space="preserve">7028766</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -14760,11 +14760,11 @@
         </is>
       </c>
       <c r="J197">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814925</t>
+          <t xml:space="preserve">311814924</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14811,35 +14811,35 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">740</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 20</t>
+          <t xml:space="preserve">Svejbækvej 5</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">8600</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025809</t>
+          <t xml:space="preserve">1461683</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J198">
-        <v>98</v>
+        <v>863</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814925</t>
+          <t xml:space="preserve">311814921</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 49</t>
+          <t xml:space="preserve">Østre Messegade 6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14901,20 +14901,20 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101016</t>
+          <t xml:space="preserve">9597370</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">70</t>
         </is>
       </c>
       <c r="J199">
-        <v>938</v>
+        <v>633</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814900</t>
+          <t xml:space="preserve">311814928</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14961,35 +14961,35 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">706</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 59</t>
+          <t xml:space="preserve">Søren Jeppesens Vej 3</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025855</t>
+          <t xml:space="preserve">4166473</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J200">
-        <v>361</v>
+        <v>1058</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814917</t>
+          <t xml:space="preserve">311816487</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-03-10</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næsborgvej 90</t>
+          <t xml:space="preserve">Alarmpladsen 2</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15051,20 +15051,20 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028766</t>
+          <t xml:space="preserve">9889328</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J201">
-        <v>218</v>
+        <v>925</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814924</t>
+          <t xml:space="preserve">311821763</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næsborgvej 90</t>
+          <t xml:space="preserve">Femagervej 37</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,20 +15126,20 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028766</t>
+          <t xml:space="preserve">2024782</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J202">
-        <v>458</v>
+        <v>276</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814924</t>
+          <t xml:space="preserve">311821760</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15186,22 +15186,22 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">740</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svejbækvej 5</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 21</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">8600</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1461683</t>
+          <t xml:space="preserve">2081592</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -15210,11 +15210,11 @@
         </is>
       </c>
       <c r="J203">
-        <v>863</v>
+        <v>303</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814921</t>
+          <t xml:space="preserve">311821754</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Messegade 6</t>
+          <t xml:space="preserve">Hvidovrevej 138</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15276,20 +15276,20 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">9597370</t>
+          <t xml:space="preserve">2025821</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J204">
-        <v>633</v>
+        <v>384</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814928</t>
+          <t xml:space="preserve">311821758</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15336,35 +15336,35 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">706</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søren Jeppesens Vej 3</t>
+          <t xml:space="preserve">Hvidovrevej 280</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4166473</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J205">
-        <v>1058</v>
+        <v>6412</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311816487</t>
+          <t xml:space="preserve">311821755</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-10</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarmpladsen 2</t>
+          <t xml:space="preserve">Hvidovrevej 98</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15426,20 +15426,20 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889328</t>
+          <t xml:space="preserve">2023815</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>925</v>
+        <v>320</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821763</t>
+          <t xml:space="preserve">311821767</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Femagervej 37</t>
+          <t xml:space="preserve">Immerkær 38</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024782</t>
+          <t xml:space="preserve">1300623</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>276</v>
+        <v>660</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821760</t>
+          <t xml:space="preserve">311821770</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 21</t>
+          <t xml:space="preserve">Lille Friheden 1</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15576,20 +15576,20 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081592</t>
+          <t xml:space="preserve">9590756</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J208">
-        <v>303</v>
+        <v>498</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821754</t>
+          <t xml:space="preserve">311821766</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 138</t>
+          <t xml:space="preserve">Østre Messegade 5</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,20 +15651,20 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025821</t>
+          <t xml:space="preserve">9889326</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J209">
-        <v>384</v>
+        <v>445</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821758</t>
+          <t xml:space="preserve">311821765</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 280</t>
+          <t xml:space="preserve">Egevolden 106</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,20 +15726,20 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J210">
-        <v>6412</v>
+        <v>237</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821755</t>
+          <t xml:space="preserve">311897781</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 98</t>
+          <t xml:space="preserve">Præstemosen 209</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023815</t>
+          <t xml:space="preserve">2025114</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,11 +15810,11 @@
         </is>
       </c>
       <c r="J211">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821767</t>
+          <t xml:space="preserve">311897780</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immerkær 38</t>
+          <t xml:space="preserve">Præstemosen 209</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,20 +15876,20 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300623</t>
+          <t xml:space="preserve">2025114</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J212">
-        <v>660</v>
+        <v>1189</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821770</t>
+          <t xml:space="preserve">311897779</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Friheden 1</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 6</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,20 +15951,20 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590756</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J213">
-        <v>498</v>
+        <v>324</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821766</t>
+          <t xml:space="preserve">311903569</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Messegade 5</t>
+          <t xml:space="preserve">Hvidovrevej 218</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,20 +16026,20 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889326</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J214">
-        <v>445</v>
+        <v>160</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821765</t>
+          <t xml:space="preserve">311903570</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevolden 106</t>
+          <t xml:space="preserve">Høvedstensvej 19</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,20 +16101,20 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J215">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897781</t>
+          <t xml:space="preserve">311903573</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemosen 209</t>
+          <t xml:space="preserve">Næsborgvej 92</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025114</t>
+          <t xml:space="preserve">2025854</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -16185,11 +16185,11 @@
         </is>
       </c>
       <c r="J216">
-        <v>319</v>
+        <v>74</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897780</t>
+          <t xml:space="preserve">311903572</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemosen 209</t>
+          <t xml:space="preserve">Strandhavevej 7</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16251,20 +16251,20 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025114</t>
+          <t xml:space="preserve">2081511</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J217">
-        <v>1189</v>
+        <v>721</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897779</t>
+          <t xml:space="preserve">311903567</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 6</t>
+          <t xml:space="preserve">Frydenhøjstien 2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,30 +16326,30 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J218">
-        <v>324</v>
+        <v>969</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903569</t>
+          <t xml:space="preserve">311930507</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 218</t>
+          <t xml:space="preserve">Frydenhøjstien 2</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16401,30 +16401,30 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J219">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903570</t>
+          <t xml:space="preserve">311930507</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 19</t>
+          <t xml:space="preserve">Frydenhøjstien 4</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16476,30 +16476,30 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J220">
-        <v>95</v>
+        <v>5857</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903573</t>
+          <t xml:space="preserve">311930507</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næsborgvej 92</t>
+          <t xml:space="preserve">Frydenhøjstien 6</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16551,30 +16551,30 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025854</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J221">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903572</t>
+          <t xml:space="preserve">311930507</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandhavevej 7</t>
+          <t xml:space="preserve">Frydenhøjstien 8</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16626,30 +16626,30 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081511</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J222">
-        <v>721</v>
+        <v>537</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903567</t>
+          <t xml:space="preserve">311930507</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
